--- a/Shared/XLS/Summon.xlsx
+++ b/Shared/XLS/Summon.xlsx
@@ -775,7 +775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -792,12 +792,11 @@
     <col min="14" max="14" width="16.625" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.125" style="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="9" style="5"/>
-    <col min="23" max="16384" width="9" style="4"/>
+    <col min="17" max="21" width="9" style="5"/>
+    <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,9 +822,8 @@
       <c r="S1" s="17"/>
       <c r="T1" s="17"/>
       <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-    </row>
-    <row r="2" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>1</v>
@@ -872,9 +870,8 @@
       <c r="P2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="14"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
@@ -921,7 +918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
       <c r="D4" s="16"/>
@@ -938,7 +935,7 @@
       <c r="O4" s="16"/>
       <c r="P4" s="16"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -955,7 +952,7 @@
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -972,7 +969,7 @@
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -989,7 +986,7 @@
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
@@ -1006,7 +1003,7 @@
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -1023,7 +1020,7 @@
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
@@ -1040,12 +1037,12 @@
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
